--- a/multi_regression/results_n_100_m_10000_d_10/figs_100/regression_result.xlsx
+++ b/multi_regression/results_n_100_m_10000_d_10/figs_100/regression_result.xlsx
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.0277 $\pm$ 0.0001</t>
+          <t>0.0364 $\pm$ 0.0003</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.0277 $\pm$ 0.0001</t>
+          <t>0.0364 $\pm$ 0.0003</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.0277 $\pm$ 0.0001</t>
+          <t>0.0364 $\pm$ 0.0003</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0277 $\pm$ 0.0001</t>
+          <t>0.0364 $\pm$ 0.0003</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0760 $\pm$ 0.0097</t>
+          <t>0.0766 $\pm$ 0.0097</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.1470 $\pm$ 0.0249</t>
+          <t>0.1561 $\pm$ 0.0192</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.1300 $\pm$ 0.0169</t>
+          <t>0.1304 $\pm$ 0.0169</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.1064 $\pm$ 0.0138</t>
+          <t>0.1069 $\pm$ 0.0138</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6485.5293 $\pm$ 1393.5673</t>
+          <t>7439.2222 $\pm$ 2680.9055</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3307.6301 $\pm$ 1681.4782</t>
+          <t>2610.6481 $\pm$ 1695.6071</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4272.5145 $\pm$ 1916.2194</t>
+          <t>4489.6541 $\pm$ 1373.3277</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5977.0174 $\pm$ 2946.3018</t>
+          <t>4252.7046 $\pm$ 2222.0471</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5913.6268 $\pm$ 2570.3549</t>
+          <t>5861.0657 $\pm$ 3181.5595</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1989.6512 $\pm$ 1957.4603</t>
+          <t>1752.6761 $\pm$ 1743.4905</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4102.8766 $\pm$ 2411.8952</t>
+          <t>5334.2985 $\pm$ 3266.9537</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5469.0204 $\pm$ 3350.5145</t>
+          <t>6505.5301 $\pm$ 2924.9042</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>249.1402 $\pm$ 5.8377</t>
+          <t>249.1402 $\pm$ 5.8376</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>482.7897 $\pm$ 7.5267</t>
+          <t>498.5605 $\pm$ 10.6992</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>430.5854 $\pm$ 9.5031</t>
+          <t>430.5853 $\pm$ 9.5031</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>351.8178 $\pm$ 7.9166</t>
+          <t>351.8178 $\pm$ 7.9165</t>
         </is>
       </c>
     </row>
@@ -603,17 +603,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>66.4842 $\pm$ 4.7251</t>
+          <t>59.5276 $\pm$ 6.2166</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>111.7931 $\pm$ 30.5389</t>
+          <t>111.7931 $\pm$ 30.5390</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>88.9160 $\pm$ 21.4621</t>
+          <t>88.9160 $\pm$ 21.4622</t>
         </is>
       </c>
     </row>
